--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2024/Aircraft_Cumulative_Statistics_2024.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2024/Aircraft_Cumulative_Statistics_2024.xlsx
@@ -296,7 +296,7 @@
         <v>328</v>
       </c>
       <c r="K2" s="0">
-        <v>1990</v>
+        <v>1990.3699999999999</v>
       </c>
       <c r="L2" s="0">
         <v>39.810000000000002</v>
@@ -337,13 +337,13 @@
         <v>329</v>
       </c>
       <c r="K3" s="0">
-        <v>2008</v>
+        <v>2007.6300000000001</v>
       </c>
       <c r="L3" s="0">
         <v>40.149999999999999</v>
       </c>
       <c r="M3" s="0">
-        <v>0.17999999999999999</v>
+        <v>0.17599999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -378,13 +378,13 @@
         <v>444</v>
       </c>
       <c r="K4" s="0">
-        <v>1903</v>
+        <v>1903.22</v>
       </c>
       <c r="L4" s="0">
         <v>28.719999999999999</v>
       </c>
       <c r="M4" s="0">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="5">
@@ -419,13 +419,13 @@
         <v>519</v>
       </c>
       <c r="K5" s="0">
-        <v>1609</v>
+        <v>1608.6199999999999</v>
       </c>
       <c r="L5" s="0">
         <v>21.449999999999999</v>
       </c>
       <c r="M5" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -460,13 +460,13 @@
         <v>332</v>
       </c>
       <c r="K6" s="0">
-        <v>2525</v>
+        <v>2525.0500000000002</v>
       </c>
       <c r="L6" s="0">
         <v>50.5</v>
       </c>
       <c r="M6" s="0">
-        <v>0.23000000000000001</v>
+        <v>0.22900000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -501,13 +501,13 @@
         <v>450</v>
       </c>
       <c r="K7" s="0">
-        <v>2451</v>
+        <v>2450.9299999999998</v>
       </c>
       <c r="L7" s="0">
         <v>37.229999999999997</v>
       </c>
       <c r="M7" s="0">
-        <v>0.14000000000000001</v>
+        <v>0.13800000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -542,13 +542,13 @@
         <v>479</v>
       </c>
       <c r="K8" s="0">
-        <v>5912</v>
+        <v>5912.04</v>
       </c>
       <c r="L8" s="0">
         <v>58.640000000000001</v>
       </c>
       <c r="M8" s="0">
-        <v>0.20999999999999999</v>
+        <v>0.20899999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -583,13 +583,13 @@
         <v>427</v>
       </c>
       <c r="K9" s="0">
-        <v>2034</v>
+        <v>2034.3499999999999</v>
       </c>
       <c r="L9" s="0">
         <v>27.010000000000002</v>
       </c>
       <c r="M9" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.10299999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -624,13 +624,13 @@
         <v>947</v>
       </c>
       <c r="K10" s="0">
-        <v>5096</v>
+        <v>5096.3000000000002</v>
       </c>
       <c r="L10" s="0">
         <v>46.770000000000003</v>
       </c>
       <c r="M10" s="0">
-        <v>0.13</v>
+        <v>0.13200000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -665,13 +665,13 @@
         <v>990</v>
       </c>
       <c r="K11" s="0">
-        <v>5291</v>
+        <v>5291.2200000000003</v>
       </c>
       <c r="L11" s="0">
         <v>38.939999999999998</v>
       </c>
       <c r="M11" s="0">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="12">
@@ -706,13 +706,13 @@
         <v>757</v>
       </c>
       <c r="K12" s="0">
-        <v>5097</v>
+        <v>5096.5299999999997</v>
       </c>
       <c r="L12" s="0">
         <v>38.950000000000003</v>
       </c>
       <c r="M12" s="0">
-        <v>0.11</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="13">
@@ -747,13 +747,13 @@
         <v>940</v>
       </c>
       <c r="K13" s="0">
-        <v>5557</v>
+        <v>5556.8699999999999</v>
       </c>
       <c r="L13" s="0">
         <v>33.880000000000003</v>
       </c>
       <c r="M13" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.091999999999999998</v>
       </c>
     </row>
     <row r="14">
@@ -788,7 +788,7 @@
         <v>921</v>
       </c>
       <c r="K14" s="0">
-        <v>4567</v>
+        <v>4566.9899999999998</v>
       </c>
       <c r="L14" s="0">
         <v>24.940000000000001</v>
@@ -829,13 +829,13 @@
         <v>1152</v>
       </c>
       <c r="K15" s="0">
-        <v>5980</v>
+        <v>5980.1899999999996</v>
       </c>
       <c r="L15" s="0">
         <v>31.809999999999999</v>
       </c>
       <c r="M15" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.084000000000000005</v>
       </c>
     </row>
     <row r="16">
@@ -870,13 +870,13 @@
         <v>1668</v>
       </c>
       <c r="K16" s="0">
-        <v>5966</v>
+        <v>5966.2299999999996</v>
       </c>
       <c r="L16" s="0">
         <v>29.879999999999999</v>
       </c>
       <c r="M16" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="17">
@@ -911,13 +911,13 @@
         <v>363</v>
       </c>
       <c r="K17" s="0">
-        <v>5394</v>
+        <v>5393.9799999999996</v>
       </c>
       <c r="L17" s="0">
         <v>47.75</v>
       </c>
       <c r="M17" s="0">
-        <v>0.17000000000000001</v>
+        <v>0.17399999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -952,13 +952,13 @@
         <v>707</v>
       </c>
       <c r="K18" s="0">
-        <v>5328</v>
+        <v>5327.9700000000003</v>
       </c>
       <c r="L18" s="0">
         <v>37.740000000000002</v>
       </c>
       <c r="M18" s="0">
-        <v>0.11</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="19">
@@ -993,13 +993,13 @@
         <v>931</v>
       </c>
       <c r="K19" s="0">
-        <v>5527</v>
+        <v>5527.1800000000003</v>
       </c>
       <c r="L19" s="0">
         <v>32.460000000000001</v>
       </c>
       <c r="M19" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.087999999999999995</v>
       </c>
     </row>
     <row r="20">
@@ -1034,7 +1034,7 @@
         <v>1005</v>
       </c>
       <c r="K20" s="0">
-        <v>4591</v>
+        <v>4591.1199999999999</v>
       </c>
       <c r="L20" s="0">
         <v>26.68</v>
@@ -1075,13 +1075,13 @@
         <v>967</v>
       </c>
       <c r="K21" s="0">
-        <v>5425</v>
+        <v>5424.6000000000004</v>
       </c>
       <c r="L21" s="0">
         <v>30.390000000000001</v>
       </c>
       <c r="M21" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="22">
@@ -1116,13 +1116,13 @@
         <v>1112</v>
       </c>
       <c r="K22" s="0">
-        <v>5628</v>
+        <v>5627.8699999999999</v>
       </c>
       <c r="L22" s="0">
         <v>31.469999999999999</v>
       </c>
       <c r="M22" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="23">
@@ -1157,13 +1157,13 @@
         <v>1528</v>
       </c>
       <c r="K23" s="0">
-        <v>4523</v>
+        <v>4522.5600000000004</v>
       </c>
       <c r="L23" s="0">
         <v>25.329999999999998</v>
       </c>
       <c r="M23" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="24">
@@ -1198,13 +1198,13 @@
         <v>1143</v>
       </c>
       <c r="K24" s="0">
-        <v>6612</v>
+        <v>6611.6999999999998</v>
       </c>
       <c r="L24" s="0">
         <v>36.020000000000003</v>
       </c>
       <c r="M24" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="25">
@@ -1239,13 +1239,13 @@
         <v>1445</v>
       </c>
       <c r="K25" s="0">
-        <v>6849</v>
+        <v>6849.1800000000003</v>
       </c>
       <c r="L25" s="0">
         <v>29.27</v>
       </c>
       <c r="M25" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.071999999999999995</v>
       </c>
     </row>
     <row r="26">
@@ -1280,13 +1280,13 @@
         <v>3345</v>
       </c>
       <c r="K26" s="0">
-        <v>8584</v>
+        <v>8584.3899999999994</v>
       </c>
       <c r="L26" s="0">
         <v>43.140000000000001</v>
       </c>
       <c r="M26" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1321,13 +1321,13 @@
         <v>3842</v>
       </c>
       <c r="K27" s="0">
-        <v>9386</v>
+        <v>9386.2399999999998</v>
       </c>
       <c r="L27" s="0">
         <v>40.219999999999999</v>
       </c>
       <c r="M27" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.085000000000000006</v>
       </c>
     </row>
     <row r="28">
@@ -1362,13 +1362,13 @@
         <v>3457</v>
       </c>
       <c r="K28" s="0">
-        <v>9590</v>
+        <v>9589.9500000000007</v>
       </c>
       <c r="L28" s="0">
         <v>36.960000000000001</v>
       </c>
       <c r="M28" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="29">
@@ -1403,13 +1403,13 @@
         <v>4074</v>
       </c>
       <c r="K29" s="0">
-        <v>9589</v>
+        <v>9589.2999999999993</v>
       </c>
       <c r="L29" s="0">
         <v>34.030000000000001</v>
       </c>
       <c r="M29" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="30">
@@ -1444,13 +1444,13 @@
         <v>4635</v>
       </c>
       <c r="K30" s="0">
-        <v>9430</v>
+        <v>9429.7800000000007</v>
       </c>
       <c r="L30" s="0">
         <v>33.579999999999998</v>
       </c>
       <c r="M30" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="31">
@@ -1485,13 +1485,13 @@
         <v>5260</v>
       </c>
       <c r="K31" s="0">
-        <v>10106</v>
+        <v>10106.16</v>
       </c>
       <c r="L31" s="0">
         <v>32.5</v>
       </c>
       <c r="M31" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="32">
@@ -1526,13 +1526,13 @@
         <v>4122</v>
       </c>
       <c r="K32" s="0">
-        <v>12112</v>
+        <v>12111.77</v>
       </c>
       <c r="L32" s="0">
         <v>51.359999999999999</v>
       </c>
       <c r="M32" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="33">
@@ -1567,13 +1567,13 @@
         <v>5214</v>
       </c>
       <c r="K33" s="0">
-        <v>10521</v>
+        <v>10521.129999999999</v>
       </c>
       <c r="L33" s="0">
         <v>39.460000000000001</v>
       </c>
       <c r="M33" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="34">
@@ -1608,13 +1608,13 @@
         <v>4370</v>
       </c>
       <c r="K34" s="0">
-        <v>10338</v>
+        <v>10337.530000000001</v>
       </c>
       <c r="L34" s="0">
         <v>32.509999999999998</v>
       </c>
       <c r="M34" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="35">
@@ -1649,7 +1649,7 @@
         <v>3833</v>
       </c>
       <c r="K35" s="0">
-        <v>12473</v>
+        <v>12472.76</v>
       </c>
       <c r="L35" s="0">
         <v>43.289999999999999</v>
@@ -1690,13 +1690,13 @@
         <v>5034</v>
       </c>
       <c r="K36" s="0">
-        <v>13545</v>
+        <v>13544.77</v>
       </c>
       <c r="L36" s="0">
         <v>41.079999999999998</v>
       </c>
       <c r="M36" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="37">
@@ -1731,13 +1731,13 @@
         <v>940</v>
       </c>
       <c r="K37" s="0">
-        <v>5393</v>
+        <v>5393.1499999999996</v>
       </c>
       <c r="L37" s="0">
         <v>33.219999999999999</v>
       </c>
       <c r="M37" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2024/Aircraft_Cumulative_Statistics_2024.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2024/Aircraft_Cumulative_Statistics_2024.xlsx
@@ -30,7 +30,7 @@
     <t>E175</t>
   </si>
   <si>
-    <t>CRJ-500</t>
+    <t>CRJ-550</t>
   </si>
   <si>
     <t>CRJ-700</t>
@@ -925,37 +925,37 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>61668268119</v>
+        <v>62399818608</v>
       </c>
       <c r="C18" s="0">
-        <v>76663491652</v>
+        <v>77621471242</v>
       </c>
       <c r="D18" s="0">
-        <v>490992</v>
+        <v>490809</v>
       </c>
       <c r="E18" s="0">
         <v>142</v>
       </c>
       <c r="F18" s="0">
-        <v>768330</v>
+        <v>777223</v>
       </c>
       <c r="G18" s="0">
-        <v>4.9199999999999999</v>
+        <v>4.9100000000000001</v>
       </c>
       <c r="H18" s="0">
         <v>9.7599999999999998</v>
       </c>
       <c r="I18" s="0">
-        <v>80.439999999999998</v>
+        <v>80.390000000000001</v>
       </c>
       <c r="J18" s="0">
         <v>707</v>
       </c>
       <c r="K18" s="0">
-        <v>5327.9700000000003</v>
+        <v>5325.3100000000004</v>
       </c>
       <c r="L18" s="0">
-        <v>37.740000000000002</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="M18" s="0">
         <v>0.106</v>
@@ -966,37 +966,37 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>147964919150</v>
+        <v>149205525291</v>
       </c>
       <c r="C19" s="0">
-        <v>178766738463</v>
+        <v>180486373227</v>
       </c>
       <c r="D19" s="0">
-        <v>580977</v>
+        <v>581483</v>
       </c>
       <c r="E19" s="0">
         <v>171</v>
       </c>
       <c r="F19" s="0">
-        <v>1128384</v>
+        <v>1139192</v>
       </c>
       <c r="G19" s="0">
         <v>3.6699999999999999</v>
       </c>
       <c r="H19" s="0">
-        <v>9.2899999999999991</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I19" s="0">
-        <v>82.769999999999996</v>
+        <v>82.670000000000002</v>
       </c>
       <c r="J19" s="0">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="K19" s="0">
-        <v>5527.1800000000003</v>
+        <v>5513.75</v>
       </c>
       <c r="L19" s="0">
-        <v>32.460000000000001</v>
+        <v>32.340000000000003</v>
       </c>
       <c r="M19" s="0">
         <v>0.087999999999999995</v>
@@ -1704,19 +1704,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>1127338610263</v>
+        <v>1129310766893</v>
       </c>
       <c r="C37" s="0">
-        <v>1351749889979</v>
+        <v>1354427504333</v>
       </c>
       <c r="D37" s="0">
-        <v>553519</v>
+        <v>553539</v>
       </c>
       <c r="E37" s="0">
         <v>143</v>
       </c>
       <c r="F37" s="0">
-        <v>8384987</v>
+        <v>8404688</v>
       </c>
       <c r="G37" s="0">
         <v>3.4300000000000002</v>
@@ -1725,16 +1725,16 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="I37" s="0">
-        <v>83.400000000000006</v>
+        <v>83.379999999999995</v>
       </c>
       <c r="J37" s="0">
         <v>940</v>
       </c>
       <c r="K37" s="0">
-        <v>5393.1499999999996</v>
+        <v>5391.4099999999999</v>
       </c>
       <c r="L37" s="0">
-        <v>33.219999999999999</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="M37" s="0">
         <v>0.085999999999999993</v>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2024/Aircraft_Cumulative_Statistics_2024.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2024/Aircraft_Cumulative_Statistics_2024.xlsx
@@ -13,35 +13,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>E145</t>
-  </si>
-  <si>
-    <t>CRJ-200</t>
-  </si>
-  <si>
-    <t>E170</t>
-  </si>
-  <si>
-    <t>E175</t>
-  </si>
-  <si>
-    <t>CRJ-550</t>
-  </si>
-  <si>
-    <t>CRJ-700</t>
-  </si>
-  <si>
-    <t>E190</t>
-  </si>
-  <si>
-    <t>CRJ-900</t>
-  </si>
-  <si>
     <t>A220-100</t>
   </si>
   <si>
@@ -52,9 +28,6 @@
   </si>
   <si>
     <t>A320</t>
-  </si>
-  <si>
-    <t>A320NEO</t>
   </si>
   <si>
     <t>A321</t>
@@ -205,7 +178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -228,40 +201,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="L1" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="M1" s="0" t="s">
         <v>39</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="L1" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="M1" s="0" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2">
@@ -269,40 +242,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>2716224662</v>
+        <v>3669794410</v>
       </c>
       <c r="C2" s="0">
-        <v>3174004715</v>
+        <v>4312388860</v>
       </c>
       <c r="D2" s="0">
-        <v>74577</v>
+        <v>266197</v>
       </c>
       <c r="E2" s="0">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="F2" s="0">
-        <v>193328</v>
+        <v>41784</v>
       </c>
       <c r="G2" s="0">
-        <v>4.54</v>
+        <v>2.5800000000000001</v>
       </c>
       <c r="H2" s="0">
-        <v>6.7400000000000002</v>
+        <v>6.9000000000000004</v>
       </c>
       <c r="I2" s="0">
-        <v>85.579999999999998</v>
+        <v>85.099999999999994</v>
       </c>
       <c r="J2" s="0">
-        <v>328</v>
+        <v>947</v>
       </c>
       <c r="K2" s="0">
-        <v>1990.3699999999999</v>
+        <v>5096.3000000000002</v>
       </c>
       <c r="L2" s="0">
-        <v>39.810000000000002</v>
+        <v>46.770000000000003</v>
       </c>
       <c r="M2" s="0">
-        <v>0.17999999999999999</v>
+        <v>0.13200000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -310,40 +283,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>1510259178</v>
+        <v>3821145710</v>
       </c>
       <c r="C3" s="0">
-        <v>1923812350</v>
+        <v>4567709819</v>
       </c>
       <c r="D3" s="0">
-        <v>41515</v>
+        <v>492741</v>
       </c>
       <c r="E3" s="0">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="F3" s="0">
-        <v>116773</v>
+        <v>34351</v>
       </c>
       <c r="G3" s="0">
-        <v>2.52</v>
+        <v>3.71</v>
       </c>
       <c r="H3" s="0">
-        <v>3.6299999999999999</v>
+        <v>10.24</v>
       </c>
       <c r="I3" s="0">
-        <v>78.5</v>
+        <v>83.659999999999997</v>
       </c>
       <c r="J3" s="0">
-        <v>329</v>
+        <v>1023</v>
       </c>
       <c r="K3" s="0">
-        <v>2007.6300000000001</v>
+        <v>5239.1000000000004</v>
       </c>
       <c r="L3" s="0">
-        <v>40.149999999999999</v>
+        <v>40.310000000000002</v>
       </c>
       <c r="M3" s="0">
-        <v>0.17599999999999999</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="4">
@@ -351,40 +324,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>2422187878</v>
+        <v>29060216670</v>
       </c>
       <c r="C4" s="0">
-        <v>2889069624</v>
+        <v>34904338393</v>
       </c>
       <c r="D4" s="0">
-        <v>46426</v>
+        <v>354431</v>
       </c>
       <c r="E4" s="0">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="F4" s="0">
-        <v>98161</v>
+        <v>366856</v>
       </c>
       <c r="G4" s="0">
-        <v>1.5800000000000001</v>
+        <v>3.73</v>
       </c>
       <c r="H4" s="0">
-        <v>2.6600000000000001</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I4" s="0">
-        <v>83.840000000000003</v>
+        <v>83.260000000000005</v>
       </c>
       <c r="J4" s="0">
-        <v>444</v>
+        <v>742</v>
       </c>
       <c r="K4" s="0">
-        <v>1903.22</v>
+        <v>5102.4099999999999</v>
       </c>
       <c r="L4" s="0">
-        <v>28.719999999999999</v>
+        <v>39.810000000000002</v>
       </c>
       <c r="M4" s="0">
-        <v>0.109</v>
+        <v>0.11799999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -392,40 +365,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>35902271223</v>
+        <v>26602156867</v>
       </c>
       <c r="C5" s="0">
-        <v>43814603727</v>
+        <v>31908635336</v>
       </c>
       <c r="D5" s="0">
-        <v>137648</v>
+        <v>462981</v>
       </c>
       <c r="E5" s="0">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="F5" s="0">
-        <v>1124576</v>
+        <v>253990</v>
       </c>
       <c r="G5" s="0">
-        <v>3.5299999999999998</v>
+        <v>3.6899999999999999</v>
       </c>
       <c r="H5" s="0">
-        <v>6.4000000000000004</v>
+        <v>8.6600000000000001</v>
       </c>
       <c r="I5" s="0">
-        <v>81.939999999999998</v>
+        <v>83.370000000000005</v>
       </c>
       <c r="J5" s="0">
-        <v>519</v>
+        <v>825</v>
       </c>
       <c r="K5" s="0">
-        <v>1608.6199999999999</v>
+        <v>5640.29</v>
       </c>
       <c r="L5" s="0">
-        <v>21.449999999999999</v>
+        <v>37.049999999999997</v>
       </c>
       <c r="M5" s="0">
-        <v>0.074999999999999997</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="6">
@@ -433,40 +406,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>846268635</v>
+        <v>80509864294</v>
       </c>
       <c r="C6" s="0">
-        <v>1026641800</v>
+        <v>92870695412</v>
       </c>
       <c r="D6" s="0">
-        <v>39916</v>
+        <v>741128</v>
       </c>
       <c r="E6" s="0">
-        <v>50</v>
+        <v>187</v>
       </c>
       <c r="F6" s="0">
-        <v>61937</v>
+        <v>466471</v>
       </c>
       <c r="G6" s="0">
-        <v>2.4100000000000001</v>
+        <v>3.7200000000000002</v>
       </c>
       <c r="H6" s="0">
-        <v>3.6299999999999999</v>
+        <v>10.66</v>
       </c>
       <c r="I6" s="0">
-        <v>82.430000000000007</v>
+        <v>86.689999999999998</v>
       </c>
       <c r="J6" s="0">
-        <v>332</v>
+        <v>1080</v>
       </c>
       <c r="K6" s="0">
-        <v>2525.0500000000002</v>
+        <v>6354.9700000000003</v>
       </c>
       <c r="L6" s="0">
-        <v>50.5</v>
+        <v>34.329999999999998</v>
       </c>
       <c r="M6" s="0">
-        <v>0.22900000000000001</v>
+        <v>0.090999999999999998</v>
       </c>
     </row>
     <row r="7">
@@ -474,40 +447,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>5480054387</v>
+        <v>48324978379</v>
       </c>
       <c r="C7" s="0">
-        <v>6956448099</v>
+        <v>55097352287</v>
       </c>
       <c r="D7" s="0">
-        <v>92236</v>
+        <v>983881</v>
       </c>
       <c r="E7" s="0">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="F7" s="0">
-        <v>234865</v>
+        <v>157014</v>
       </c>
       <c r="G7" s="0">
-        <v>3.1099999999999999</v>
+        <v>2.7999999999999998</v>
       </c>
       <c r="H7" s="0">
-        <v>5.21</v>
+        <v>12</v>
       </c>
       <c r="I7" s="0">
-        <v>78.780000000000001</v>
+        <v>87.709999999999994</v>
       </c>
       <c r="J7" s="0">
-        <v>450</v>
+        <v>1799</v>
       </c>
       <c r="K7" s="0">
-        <v>2450.9299999999998</v>
+        <v>6455.04</v>
       </c>
       <c r="L7" s="0">
-        <v>37.229999999999997</v>
+        <v>33.090000000000003</v>
       </c>
       <c r="M7" s="0">
-        <v>0.13800000000000001</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -515,40 +488,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>1836612063</v>
+        <v>5835260728</v>
       </c>
       <c r="C8" s="0">
-        <v>2277654916</v>
+        <v>6816934834</v>
       </c>
       <c r="D8" s="0">
-        <v>170483</v>
+        <v>236699</v>
       </c>
       <c r="E8" s="0">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F8" s="0">
-        <v>47079</v>
+        <v>137456</v>
       </c>
       <c r="G8" s="0">
-        <v>3.52</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="H8" s="0">
-        <v>6.0199999999999996</v>
+        <v>7.25</v>
       </c>
       <c r="I8" s="0">
-        <v>80.640000000000001</v>
+        <v>85.599999999999994</v>
       </c>
       <c r="J8" s="0">
-        <v>479</v>
+        <v>451</v>
       </c>
       <c r="K8" s="0">
-        <v>5912.04</v>
+        <v>5246.0500000000002</v>
       </c>
       <c r="L8" s="0">
-        <v>58.640000000000001</v>
+        <v>47.700000000000003</v>
       </c>
       <c r="M8" s="0">
-        <v>0.20899999999999999</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="9">
@@ -556,40 +529,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>11639278643</v>
+        <v>4919657605</v>
       </c>
       <c r="C9" s="0">
-        <v>14152222010</v>
+        <v>5777279676</v>
       </c>
       <c r="D9" s="0">
-        <v>147496</v>
+        <v>394085</v>
       </c>
       <c r="E9" s="0">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="F9" s="0">
-        <v>439639</v>
+        <v>48250</v>
       </c>
       <c r="G9" s="0">
-        <v>4.5800000000000001</v>
+        <v>3.29</v>
       </c>
       <c r="H9" s="0">
-        <v>7.46</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I9" s="0">
-        <v>82.239999999999995</v>
+        <v>85.159999999999997</v>
       </c>
       <c r="J9" s="0">
-        <v>427</v>
+        <v>950</v>
       </c>
       <c r="K9" s="0">
-        <v>2034.3499999999999</v>
+        <v>8482.6700000000001</v>
       </c>
       <c r="L9" s="0">
-        <v>27.010000000000002</v>
+        <v>67.319999999999993</v>
       </c>
       <c r="M9" s="0">
-        <v>0.10299999999999999</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="10">
@@ -597,40 +570,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>3669794410</v>
+        <v>90486015201</v>
       </c>
       <c r="C10" s="0">
-        <v>4312388860</v>
+        <v>107710341185</v>
       </c>
       <c r="D10" s="0">
-        <v>266197</v>
+        <v>566718</v>
       </c>
       <c r="E10" s="0">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="F10" s="0">
-        <v>41784</v>
+        <v>672573</v>
       </c>
       <c r="G10" s="0">
-        <v>2.5800000000000001</v>
+        <v>3.54</v>
       </c>
       <c r="H10" s="0">
-        <v>6.9000000000000004</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I10" s="0">
-        <v>85.099999999999994</v>
+        <v>84.010000000000005</v>
       </c>
       <c r="J10" s="0">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="K10" s="0">
-        <v>5096.3000000000002</v>
+        <v>5645.9200000000001</v>
       </c>
       <c r="L10" s="0">
-        <v>46.770000000000003</v>
+        <v>33.450000000000003</v>
       </c>
       <c r="M10" s="0">
-        <v>0.13200000000000001</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -638,40 +611,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>11788262339</v>
+        <v>36481890124</v>
       </c>
       <c r="C11" s="0">
-        <v>14510541074</v>
+        <v>42762776643</v>
       </c>
       <c r="D11" s="0">
-        <v>484169</v>
+        <v>745906</v>
       </c>
       <c r="E11" s="0">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="F11" s="0">
-        <v>107898</v>
+        <v>193539</v>
       </c>
       <c r="G11" s="0">
-        <v>3.6000000000000001</v>
+        <v>3.3799999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>9.8399999999999999</v>
+        <v>11.289999999999999</v>
       </c>
       <c r="I11" s="0">
-        <v>81.239999999999995</v>
+        <v>85.310000000000002</v>
       </c>
       <c r="J11" s="0">
-        <v>990</v>
+        <v>1314</v>
       </c>
       <c r="K11" s="0">
-        <v>5291.2200000000003</v>
+        <v>5058.6199999999999</v>
       </c>
       <c r="L11" s="0">
-        <v>38.939999999999998</v>
+        <v>30.07</v>
       </c>
       <c r="M11" s="0">
-        <v>0.108</v>
+        <v>0.076999999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -679,40 +652,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>33853921230</v>
+        <v>1939041943</v>
       </c>
       <c r="C12" s="0">
-        <v>40582623784</v>
+        <v>2353910860</v>
       </c>
       <c r="D12" s="0">
-        <v>355551</v>
+        <v>534980</v>
       </c>
       <c r="E12" s="0">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="F12" s="0">
-        <v>408878</v>
+        <v>13497</v>
       </c>
       <c r="G12" s="0">
-        <v>3.5800000000000001</v>
+        <v>3.0699999999999998</v>
       </c>
       <c r="H12" s="0">
-        <v>7.96</v>
+        <v>8.1199999999999992</v>
       </c>
       <c r="I12" s="0">
-        <v>83.420000000000002</v>
+        <v>82.379999999999995</v>
       </c>
       <c r="J12" s="0">
-        <v>757</v>
+        <v>974</v>
       </c>
       <c r="K12" s="0">
-        <v>5096.5299999999997</v>
+        <v>5772.0699999999997</v>
       </c>
       <c r="L12" s="0">
-        <v>38.950000000000003</v>
+        <v>32.25</v>
       </c>
       <c r="M12" s="0">
-        <v>0.114</v>
+        <v>0.087999999999999995</v>
       </c>
     </row>
     <row r="13">
@@ -720,40 +693,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>77604669135</v>
+        <v>59488055074</v>
       </c>
       <c r="C13" s="0">
-        <v>93717782656</v>
+        <v>69310147870</v>
       </c>
       <c r="D13" s="0">
-        <v>530378</v>
+        <v>639098</v>
       </c>
       <c r="E13" s="0">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="F13" s="0">
-        <v>606894</v>
+        <v>382047</v>
       </c>
       <c r="G13" s="0">
-        <v>3.4300000000000002</v>
+        <v>3.52</v>
       </c>
       <c r="H13" s="0">
-        <v>8.8100000000000005</v>
+        <v>9.5199999999999996</v>
       </c>
       <c r="I13" s="0">
-        <v>82.810000000000002</v>
+        <v>85.829999999999998</v>
       </c>
       <c r="J13" s="0">
-        <v>940</v>
+        <v>1012</v>
       </c>
       <c r="K13" s="0">
-        <v>5556.8699999999999</v>
+        <v>5780.25</v>
       </c>
       <c r="L13" s="0">
-        <v>33.880000000000003</v>
+        <v>32.280000000000001</v>
       </c>
       <c r="M13" s="0">
-        <v>0.091999999999999998</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="14">
@@ -761,40 +734,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>32214615227</v>
+        <v>19574188093</v>
       </c>
       <c r="C14" s="0">
-        <v>39862426380</v>
+        <v>22755095760</v>
       </c>
       <c r="D14" s="0">
-        <v>649543</v>
+        <v>770576</v>
       </c>
       <c r="E14" s="0">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F14" s="0">
-        <v>236507</v>
+        <v>91004</v>
       </c>
       <c r="G14" s="0">
-        <v>3.8500000000000001</v>
+        <v>3.0800000000000001</v>
       </c>
       <c r="H14" s="0">
-        <v>9.9100000000000001</v>
+        <v>10.82</v>
       </c>
       <c r="I14" s="0">
-        <v>80.810000000000002</v>
+        <v>86.019999999999996</v>
       </c>
       <c r="J14" s="0">
-        <v>921</v>
+        <v>1397</v>
       </c>
       <c r="K14" s="0">
-        <v>4566.9899999999998</v>
+        <v>4905.3800000000001</v>
       </c>
       <c r="L14" s="0">
-        <v>24.940000000000001</v>
+        <v>27.399999999999999</v>
       </c>
       <c r="M14" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="15">
@@ -802,40 +775,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>110642958838</v>
+        <v>27203057966</v>
       </c>
       <c r="C15" s="0">
-        <v>129208206120</v>
+        <v>31118577568</v>
       </c>
       <c r="D15" s="0">
-        <v>773702</v>
+        <v>641620</v>
       </c>
       <c r="E15" s="0">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F15" s="0">
-        <v>599908</v>
+        <v>149105</v>
       </c>
       <c r="G15" s="0">
-        <v>3.5899999999999999</v>
+        <v>3.0699999999999998</v>
       </c>
       <c r="H15" s="0">
-        <v>10.83</v>
+        <v>9.0899999999999999</v>
       </c>
       <c r="I15" s="0">
-        <v>85.629999999999995</v>
+        <v>87.420000000000002</v>
       </c>
       <c r="J15" s="0">
-        <v>1152</v>
+        <v>1143</v>
       </c>
       <c r="K15" s="0">
-        <v>5980.1899999999996</v>
+        <v>6611.6999999999998</v>
       </c>
       <c r="L15" s="0">
-        <v>31.809999999999999</v>
+        <v>36.020000000000003</v>
       </c>
       <c r="M15" s="0">
-        <v>0.084000000000000005</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="16">
@@ -843,40 +816,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>73577031255</v>
+        <v>9570375826</v>
       </c>
       <c r="C16" s="0">
-        <v>87107370555</v>
+        <v>10969869623</v>
       </c>
       <c r="D16" s="0">
-        <v>915667</v>
+        <v>816211</v>
       </c>
       <c r="E16" s="0">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="F16" s="0">
-        <v>263291</v>
+        <v>32436</v>
       </c>
       <c r="G16" s="0">
-        <v>2.77</v>
+        <v>2.4100000000000001</v>
       </c>
       <c r="H16" s="0">
-        <v>11.140000000000001</v>
+        <v>8.5899999999999999</v>
       </c>
       <c r="I16" s="0">
-        <v>84.469999999999999</v>
+        <v>87.239999999999995</v>
       </c>
       <c r="J16" s="0">
-        <v>1668</v>
+        <v>1445</v>
       </c>
       <c r="K16" s="0">
-        <v>5966.2299999999996</v>
+        <v>6849.1800000000003</v>
       </c>
       <c r="L16" s="0">
-        <v>29.879999999999999</v>
+        <v>29.27</v>
       </c>
       <c r="M16" s="0">
-        <v>0.072999999999999995</v>
+        <v>0.071999999999999995</v>
       </c>
     </row>
     <row r="17">
@@ -884,40 +857,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>6567577439</v>
+        <v>25091924185</v>
       </c>
       <c r="C17" s="0">
-        <v>7777584178</v>
+        <v>29204637089</v>
       </c>
       <c r="D17" s="0">
-        <v>217616</v>
+        <v>1015107</v>
       </c>
       <c r="E17" s="0">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="F17" s="0">
-        <v>191343</v>
+        <v>43872</v>
       </c>
       <c r="G17" s="0">
-        <v>5.3499999999999996</v>
+        <v>1.52</v>
       </c>
       <c r="H17" s="0">
-        <v>7</v>
+        <v>11.01</v>
       </c>
       <c r="I17" s="0">
-        <v>84.439999999999998</v>
+        <v>85.920000000000002</v>
       </c>
       <c r="J17" s="0">
-        <v>363</v>
+        <v>3345</v>
       </c>
       <c r="K17" s="0">
-        <v>5393.9799999999996</v>
+        <v>8584.3899999999994</v>
       </c>
       <c r="L17" s="0">
-        <v>47.75</v>
+        <v>43.140000000000001</v>
       </c>
       <c r="M17" s="0">
-        <v>0.17399999999999999</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -925,40 +898,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>62399818608</v>
+        <v>15521428798</v>
       </c>
       <c r="C18" s="0">
-        <v>77621471242</v>
+        <v>18131997207</v>
       </c>
       <c r="D18" s="0">
-        <v>490809</v>
+        <v>1351118</v>
       </c>
       <c r="E18" s="0">
-        <v>142</v>
+        <v>233</v>
       </c>
       <c r="F18" s="0">
-        <v>777223</v>
+        <v>20223</v>
       </c>
       <c r="G18" s="0">
-        <v>4.9100000000000001</v>
+        <v>1.51</v>
       </c>
       <c r="H18" s="0">
-        <v>9.7599999999999998</v>
+        <v>12.210000000000001</v>
       </c>
       <c r="I18" s="0">
-        <v>80.390000000000001</v>
+        <v>85.599999999999994</v>
       </c>
       <c r="J18" s="0">
-        <v>707</v>
+        <v>3842</v>
       </c>
       <c r="K18" s="0">
-        <v>5325.3100000000004</v>
+        <v>9386.2399999999998</v>
       </c>
       <c r="L18" s="0">
-        <v>37.700000000000003</v>
+        <v>40.219999999999999</v>
       </c>
       <c r="M18" s="0">
-        <v>0.106</v>
+        <v>0.085000000000000006</v>
       </c>
     </row>
     <row r="19">
@@ -966,40 +939,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>149205525291</v>
+        <v>4616922311</v>
       </c>
       <c r="C19" s="0">
-        <v>180486373227</v>
+        <v>5621362154</v>
       </c>
       <c r="D19" s="0">
-        <v>581483</v>
+        <v>1423130</v>
       </c>
       <c r="E19" s="0">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="F19" s="0">
-        <v>1139192</v>
+        <v>6290</v>
       </c>
       <c r="G19" s="0">
-        <v>3.6699999999999999</v>
+        <v>1.5900000000000001</v>
       </c>
       <c r="H19" s="0">
-        <v>9.3000000000000007</v>
+        <v>13.41</v>
       </c>
       <c r="I19" s="0">
-        <v>82.670000000000002</v>
+        <v>82.129999999999995</v>
       </c>
       <c r="J19" s="0">
-        <v>930</v>
+        <v>4030</v>
       </c>
       <c r="K19" s="0">
-        <v>5513.75</v>
+        <v>9396.8999999999996</v>
       </c>
       <c r="L19" s="0">
-        <v>32.340000000000003</v>
+        <v>42.369999999999997</v>
       </c>
       <c r="M19" s="0">
-        <v>0.087999999999999995</v>
+        <v>0.088999999999999996</v>
       </c>
     </row>
     <row r="20">
@@ -1007,40 +980,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>84443620517</v>
+        <v>18031272799</v>
       </c>
       <c r="C20" s="0">
-        <v>102015117877</v>
+        <v>20860706823</v>
       </c>
       <c r="D20" s="0">
-        <v>707211</v>
+        <v>1869239</v>
       </c>
       <c r="E20" s="0">
-        <v>173</v>
+        <v>282</v>
       </c>
       <c r="F20" s="0">
-        <v>590236</v>
+        <v>18172</v>
       </c>
       <c r="G20" s="0">
-        <v>4.0899999999999999</v>
+        <v>1.6299999999999999</v>
       </c>
       <c r="H20" s="0">
-        <v>10.76</v>
+        <v>13.789999999999999</v>
       </c>
       <c r="I20" s="0">
-        <v>82.780000000000001</v>
+        <v>86.439999999999998</v>
       </c>
       <c r="J20" s="0">
-        <v>1005</v>
+        <v>4074</v>
       </c>
       <c r="K20" s="0">
-        <v>4591.1199999999999</v>
+        <v>9589.2999999999993</v>
       </c>
       <c r="L20" s="0">
-        <v>26.68</v>
+        <v>34.030000000000001</v>
       </c>
       <c r="M20" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="21">
@@ -1048,40 +1021,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>3888526682</v>
+        <v>16388511876</v>
       </c>
       <c r="C21" s="0">
-        <v>4739816808</v>
+        <v>19936403508</v>
       </c>
       <c r="D21" s="0">
-        <v>575919</v>
+        <v>1929952</v>
       </c>
       <c r="E21" s="0">
-        <v>178</v>
+        <v>281</v>
       </c>
       <c r="F21" s="0">
-        <v>27448</v>
+        <v>15317</v>
       </c>
       <c r="G21" s="0">
-        <v>3.3399999999999999</v>
+        <v>1.48</v>
       </c>
       <c r="H21" s="0">
-        <v>8.8599999999999994</v>
+        <v>14.220000000000001</v>
       </c>
       <c r="I21" s="0">
-        <v>82.040000000000006</v>
+        <v>82.200000000000003</v>
       </c>
       <c r="J21" s="0">
-        <v>967</v>
+        <v>4635</v>
       </c>
       <c r="K21" s="0">
-        <v>5424.6000000000004</v>
+        <v>9148.6399999999994</v>
       </c>
       <c r="L21" s="0">
-        <v>30.390000000000001</v>
+        <v>32.579999999999998</v>
       </c>
       <c r="M21" s="0">
-        <v>0.083000000000000004</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="22">
@@ -1089,40 +1062,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>79853304869</v>
+        <v>19675137613</v>
       </c>
       <c r="C22" s="0">
-        <v>93531503922</v>
+        <v>23852719215</v>
       </c>
       <c r="D22" s="0">
-        <v>680873</v>
+        <v>2127807</v>
       </c>
       <c r="E22" s="0">
-        <v>179</v>
+        <v>314</v>
       </c>
       <c r="F22" s="0">
-        <v>470268</v>
+        <v>14588</v>
       </c>
       <c r="G22" s="0">
-        <v>3.4199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="H22" s="0">
-        <v>9.9499999999999993</v>
+        <v>13.67</v>
       </c>
       <c r="I22" s="0">
-        <v>85.379999999999995</v>
+        <v>82.489999999999995</v>
       </c>
       <c r="J22" s="0">
-        <v>1112</v>
+        <v>5260</v>
       </c>
       <c r="K22" s="0">
-        <v>5627.8699999999999</v>
+        <v>10106.16</v>
       </c>
       <c r="L22" s="0">
-        <v>31.469999999999999</v>
+        <v>32.5</v>
       </c>
       <c r="M22" s="0">
-        <v>0.082000000000000003</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="23">
@@ -1130,40 +1103,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>37631753976</v>
+        <v>20712015592</v>
       </c>
       <c r="C23" s="0">
-        <v>44111877876</v>
+        <v>24270475668</v>
       </c>
       <c r="D23" s="0">
-        <v>809095</v>
+        <v>1353624</v>
       </c>
       <c r="E23" s="0">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="F23" s="0">
-        <v>161671</v>
+        <v>24970</v>
       </c>
       <c r="G23" s="0">
-        <v>2.9700000000000002</v>
+        <v>1.3899999999999999</v>
       </c>
       <c r="H23" s="0">
-        <v>11.17</v>
+        <v>11.58</v>
       </c>
       <c r="I23" s="0">
-        <v>85.310000000000002</v>
+        <v>85.340000000000003</v>
       </c>
       <c r="J23" s="0">
-        <v>1528</v>
+        <v>4122</v>
       </c>
       <c r="K23" s="0">
-        <v>4522.5600000000004</v>
+        <v>12111.77</v>
       </c>
       <c r="L23" s="0">
-        <v>25.329999999999998</v>
+        <v>51.359999999999999</v>
       </c>
       <c r="M23" s="0">
-        <v>0.062</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="24">
@@ -1171,40 +1144,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>27203057966</v>
+        <v>31933128270</v>
       </c>
       <c r="C24" s="0">
-        <v>31118577568</v>
+        <v>39389503740</v>
       </c>
       <c r="D24" s="0">
-        <v>641620</v>
+        <v>1783137</v>
       </c>
       <c r="E24" s="0">
-        <v>187</v>
+        <v>268</v>
       </c>
       <c r="F24" s="0">
-        <v>149105</v>
+        <v>27968</v>
       </c>
       <c r="G24" s="0">
-        <v>3.0699999999999998</v>
+        <v>1.27</v>
       </c>
       <c r="H24" s="0">
-        <v>9.0899999999999999</v>
+        <v>13.300000000000001</v>
       </c>
       <c r="I24" s="0">
-        <v>87.420000000000002</v>
+        <v>81.069999999999993</v>
       </c>
       <c r="J24" s="0">
-        <v>1143</v>
+        <v>5298</v>
       </c>
       <c r="K24" s="0">
-        <v>6611.6999999999998</v>
+        <v>10713</v>
       </c>
       <c r="L24" s="0">
-        <v>36.020000000000003</v>
+        <v>40.270000000000003</v>
       </c>
       <c r="M24" s="0">
-        <v>0.094</v>
+        <v>0.080000000000000002</v>
       </c>
     </row>
     <row r="25">
@@ -1212,40 +1185,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>9570375826</v>
+        <v>13247538486</v>
       </c>
       <c r="C25" s="0">
-        <v>10969869623</v>
+        <v>15859644528</v>
       </c>
       <c r="D25" s="0">
-        <v>816211</v>
+        <v>2062373</v>
       </c>
       <c r="E25" s="0">
-        <v>234</v>
+        <v>318</v>
       </c>
       <c r="F25" s="0">
-        <v>32436</v>
+        <v>11413</v>
       </c>
       <c r="G25" s="0">
-        <v>2.4100000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="H25" s="0">
-        <v>8.5899999999999999</v>
+        <v>13</v>
       </c>
       <c r="I25" s="0">
-        <v>87.239999999999995</v>
+        <v>83.530000000000001</v>
       </c>
       <c r="J25" s="0">
-        <v>1445</v>
+        <v>4370</v>
       </c>
       <c r="K25" s="0">
-        <v>6849.1800000000003</v>
+        <v>9809.6100000000006</v>
       </c>
       <c r="L25" s="0">
-        <v>29.27</v>
+        <v>30.850000000000001</v>
       </c>
       <c r="M25" s="0">
-        <v>0.071999999999999995</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="26">
@@ -1253,40 +1226,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>25091924185</v>
+        <v>58635478754</v>
       </c>
       <c r="C26" s="0">
-        <v>29204637089</v>
+        <v>71075547892</v>
       </c>
       <c r="D26" s="0">
-        <v>1015107</v>
+        <v>1605501</v>
       </c>
       <c r="E26" s="0">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="F26" s="0">
-        <v>43872</v>
+        <v>64582</v>
       </c>
       <c r="G26" s="0">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="H26" s="0">
-        <v>11.01</v>
+        <v>11.52</v>
       </c>
       <c r="I26" s="0">
-        <v>85.920000000000002</v>
+        <v>82.5</v>
       </c>
       <c r="J26" s="0">
-        <v>3345</v>
+        <v>3833</v>
       </c>
       <c r="K26" s="0">
-        <v>8584.3899999999994</v>
+        <v>12472.76</v>
       </c>
       <c r="L26" s="0">
-        <v>43.140000000000001</v>
+        <v>43.289999999999999</v>
       </c>
       <c r="M26" s="0">
-        <v>0.092999999999999999</v>
+        <v>0.089999999999999997</v>
       </c>
     </row>
     <row r="27">
@@ -1294,40 +1267,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>15521428798</v>
+        <v>26384293256</v>
       </c>
       <c r="C27" s="0">
-        <v>18131997207</v>
+        <v>33371601658</v>
       </c>
       <c r="D27" s="0">
-        <v>1351118</v>
+        <v>2172630</v>
       </c>
       <c r="E27" s="0">
-        <v>233</v>
+        <v>328</v>
       </c>
       <c r="F27" s="0">
-        <v>20223</v>
+        <v>20084</v>
       </c>
       <c r="G27" s="0">
-        <v>1.51</v>
+        <v>1.3100000000000001</v>
       </c>
       <c r="H27" s="0">
-        <v>12.210000000000001</v>
+        <v>13.19</v>
       </c>
       <c r="I27" s="0">
-        <v>85.599999999999994</v>
+        <v>79.060000000000002</v>
       </c>
       <c r="J27" s="0">
-        <v>3842</v>
+        <v>5034</v>
       </c>
       <c r="K27" s="0">
-        <v>9386.2399999999998</v>
+        <v>13544.77</v>
       </c>
       <c r="L27" s="0">
-        <v>40.219999999999999</v>
+        <v>41.079999999999998</v>
       </c>
       <c r="M27" s="0">
-        <v>0.085000000000000006</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="28">
@@ -1335,409 +1308,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>16529319851</v>
+        <v>697723350830</v>
       </c>
       <c r="C28" s="0">
-        <v>19822733614</v>
+        <v>824810653608</v>
       </c>
       <c r="D28" s="0">
-        <v>1558391</v>
+        <v>781418</v>
       </c>
       <c r="E28" s="0">
-        <v>262</v>
+        <v>174</v>
       </c>
       <c r="F28" s="0">
-        <v>22119</v>
+        <v>3307852</v>
       </c>
       <c r="G28" s="0">
-        <v>1.74</v>
+        <v>3.1299999999999999</v>
       </c>
       <c r="H28" s="0">
-        <v>12.74</v>
+        <v>10.06</v>
       </c>
       <c r="I28" s="0">
-        <v>83.390000000000001</v>
+        <v>84.590000000000003</v>
       </c>
       <c r="J28" s="0">
-        <v>3457</v>
+        <v>1272</v>
       </c>
       <c r="K28" s="0">
-        <v>9589.9500000000007</v>
+        <v>6889.1099999999997</v>
       </c>
       <c r="L28" s="0">
-        <v>36.960000000000001</v>
+        <v>36.240000000000002</v>
       </c>
       <c r="M28" s="0">
-        <v>0.078</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="0">
-        <v>18031272799</v>
-      </c>
-      <c r="C29" s="0">
-        <v>20860706823</v>
-      </c>
-      <c r="D29" s="0">
-        <v>1869239</v>
-      </c>
-      <c r="E29" s="0">
-        <v>282</v>
-      </c>
-      <c r="F29" s="0">
-        <v>18172</v>
-      </c>
-      <c r="G29" s="0">
-        <v>1.6299999999999999</v>
-      </c>
-      <c r="H29" s="0">
-        <v>13.789999999999999</v>
-      </c>
-      <c r="I29" s="0">
-        <v>86.439999999999998</v>
-      </c>
-      <c r="J29" s="0">
-        <v>4074</v>
-      </c>
-      <c r="K29" s="0">
-        <v>9589.2999999999993</v>
-      </c>
-      <c r="L29" s="0">
-        <v>34.030000000000001</v>
-      </c>
-      <c r="M29" s="0">
-        <v>0.070999999999999994</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="0">
-        <v>16388511876</v>
-      </c>
-      <c r="C30" s="0">
-        <v>19936403508</v>
-      </c>
-      <c r="D30" s="0">
-        <v>1814049</v>
-      </c>
-      <c r="E30" s="0">
-        <v>281</v>
-      </c>
-      <c r="F30" s="0">
-        <v>15317</v>
-      </c>
-      <c r="G30" s="0">
-        <v>1.3899999999999999</v>
-      </c>
-      <c r="H30" s="0">
-        <v>13.369999999999999</v>
-      </c>
-      <c r="I30" s="0">
-        <v>82.200000000000003</v>
-      </c>
-      <c r="J30" s="0">
-        <v>4635</v>
-      </c>
-      <c r="K30" s="0">
-        <v>9429.7800000000007</v>
-      </c>
-      <c r="L30" s="0">
-        <v>33.579999999999998</v>
-      </c>
-      <c r="M30" s="0">
-        <v>0.069000000000000006</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="0">
-        <v>19675137613</v>
-      </c>
-      <c r="C31" s="0">
-        <v>23852719215</v>
-      </c>
-      <c r="D31" s="0">
-        <v>2127807</v>
-      </c>
-      <c r="E31" s="0">
-        <v>314</v>
-      </c>
-      <c r="F31" s="0">
-        <v>14588</v>
-      </c>
-      <c r="G31" s="0">
-        <v>1.3</v>
-      </c>
-      <c r="H31" s="0">
-        <v>13.67</v>
-      </c>
-      <c r="I31" s="0">
-        <v>82.489999999999995</v>
-      </c>
-      <c r="J31" s="0">
-        <v>5260</v>
-      </c>
-      <c r="K31" s="0">
-        <v>10106.16</v>
-      </c>
-      <c r="L31" s="0">
-        <v>32.5</v>
-      </c>
-      <c r="M31" s="0">
-        <v>0.065000000000000002</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="0">
-        <v>20712015592</v>
-      </c>
-      <c r="C32" s="0">
-        <v>24270475668</v>
-      </c>
-      <c r="D32" s="0">
-        <v>1353624</v>
-      </c>
-      <c r="E32" s="0">
-        <v>236</v>
-      </c>
-      <c r="F32" s="0">
-        <v>24970</v>
-      </c>
-      <c r="G32" s="0">
-        <v>1.3899999999999999</v>
-      </c>
-      <c r="H32" s="0">
-        <v>11.58</v>
-      </c>
-      <c r="I32" s="0">
-        <v>85.340000000000003</v>
-      </c>
-      <c r="J32" s="0">
-        <v>4122</v>
-      </c>
-      <c r="K32" s="0">
-        <v>12111.77</v>
-      </c>
-      <c r="L32" s="0">
-        <v>51.359999999999999</v>
-      </c>
-      <c r="M32" s="0">
-        <v>0.104</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="0">
-        <v>32625875406</v>
-      </c>
-      <c r="C33" s="0">
-        <v>40153048140</v>
-      </c>
-      <c r="D33" s="0">
-        <v>1817702</v>
-      </c>
-      <c r="E33" s="0">
-        <v>269</v>
-      </c>
-      <c r="F33" s="0">
-        <v>28908</v>
-      </c>
-      <c r="G33" s="0">
-        <v>1.3100000000000001</v>
-      </c>
-      <c r="H33" s="0">
-        <v>13.539999999999999</v>
-      </c>
-      <c r="I33" s="0">
-        <v>81.25</v>
-      </c>
-      <c r="J33" s="0">
-        <v>5214</v>
-      </c>
-      <c r="K33" s="0">
-        <v>10521.129999999999</v>
-      </c>
-      <c r="L33" s="0">
-        <v>39.460000000000001</v>
-      </c>
-      <c r="M33" s="0">
-        <v>0.078</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="0">
-        <v>13247538486</v>
-      </c>
-      <c r="C34" s="0">
-        <v>15859644528</v>
-      </c>
-      <c r="D34" s="0">
-        <v>2010094</v>
-      </c>
-      <c r="E34" s="0">
-        <v>318</v>
-      </c>
-      <c r="F34" s="0">
-        <v>11413</v>
-      </c>
-      <c r="G34" s="0">
-        <v>1.45</v>
-      </c>
-      <c r="H34" s="0">
-        <v>12.67</v>
-      </c>
-      <c r="I34" s="0">
-        <v>83.530000000000001</v>
-      </c>
-      <c r="J34" s="0">
-        <v>4370</v>
-      </c>
-      <c r="K34" s="0">
-        <v>10337.530000000001</v>
-      </c>
-      <c r="L34" s="0">
-        <v>32.509999999999998</v>
-      </c>
-      <c r="M34" s="0">
-        <v>0.065000000000000002</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="0">
-        <v>58635478754</v>
-      </c>
-      <c r="C35" s="0">
-        <v>71075547892</v>
-      </c>
-      <c r="D35" s="0">
-        <v>1605501</v>
-      </c>
-      <c r="E35" s="0">
-        <v>297</v>
-      </c>
-      <c r="F35" s="0">
-        <v>64582</v>
-      </c>
-      <c r="G35" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="H35" s="0">
-        <v>11.52</v>
-      </c>
-      <c r="I35" s="0">
-        <v>82.5</v>
-      </c>
-      <c r="J35" s="0">
-        <v>3833</v>
-      </c>
-      <c r="K35" s="0">
-        <v>12472.76</v>
-      </c>
-      <c r="L35" s="0">
-        <v>43.289999999999999</v>
-      </c>
-      <c r="M35" s="0">
-        <v>0.089999999999999997</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="0">
-        <v>26384293256</v>
-      </c>
-      <c r="C36" s="0">
-        <v>33371601658</v>
-      </c>
-      <c r="D36" s="0">
-        <v>2172630</v>
-      </c>
-      <c r="E36" s="0">
-        <v>328</v>
-      </c>
-      <c r="F36" s="0">
-        <v>20084</v>
-      </c>
-      <c r="G36" s="0">
-        <v>1.3100000000000001</v>
-      </c>
-      <c r="H36" s="0">
-        <v>13.19</v>
-      </c>
-      <c r="I36" s="0">
-        <v>79.060000000000002</v>
-      </c>
-      <c r="J36" s="0">
-        <v>5034</v>
-      </c>
-      <c r="K36" s="0">
-        <v>13544.77</v>
-      </c>
-      <c r="L36" s="0">
-        <v>41.079999999999998</v>
-      </c>
-      <c r="M36" s="0">
-        <v>0.082000000000000003</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="0">
-        <v>1129310766893</v>
-      </c>
-      <c r="C37" s="0">
-        <v>1354427504333</v>
-      </c>
-      <c r="D37" s="0">
-        <v>553539</v>
-      </c>
-      <c r="E37" s="0">
-        <v>143</v>
-      </c>
-      <c r="F37" s="0">
-        <v>8404688</v>
-      </c>
-      <c r="G37" s="0">
-        <v>3.4300000000000002</v>
-      </c>
-      <c r="H37" s="0">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="I37" s="0">
-        <v>83.379999999999995</v>
-      </c>
-      <c r="J37" s="0">
-        <v>940</v>
-      </c>
-      <c r="K37" s="0">
-        <v>5391.4099999999999</v>
-      </c>
-      <c r="L37" s="0">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="M37" s="0">
-        <v>0.085999999999999993</v>
+        <v>0.088999999999999996</v>
       </c>
     </row>
   </sheetData>
